--- a/TestData/ERpExcelData.xlsx
+++ b/TestData/ERpExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mahesh_Python\FrameWork_POM\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346CCDEE-3EC6-4BFD-99B9-1A0B96C07F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB0E44A-F9B6-4BD9-978A-18381A85A82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10920" yWindow="1248" windowWidth="10488" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="suppliers" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>suppliername</t>
   </si>
@@ -245,12 +245,6 @@
     <t>aa</t>
   </si>
   <si>
-    <t>akbar</t>
-  </si>
-  <si>
-    <t>mahesh</t>
-  </si>
-  <si>
     <t>mahi</t>
   </si>
   <si>
@@ -263,9 +257,6 @@
     <t>mani</t>
   </si>
   <si>
-    <t>item</t>
-  </si>
-  <si>
     <t>Stock-000000055</t>
   </si>
   <si>
@@ -297,6 +288,21 @@
   </si>
   <si>
     <t>Sellingprice</t>
+  </si>
+  <si>
+    <t>First Category</t>
+  </si>
+  <si>
+    <t>Second Category</t>
+  </si>
+  <si>
+    <t>Fourth Category</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Third Category</t>
   </si>
 </sst>
 </file>
@@ -1027,25 +1033,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" t="s">
         <v>83</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>84</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>85</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>86</v>
-      </c>
-      <c r="E1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" t="s">
-        <v>89</v>
       </c>
       <c r="H1" t="s">
         <v>8</v>
@@ -1053,19 +1059,19 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -1079,19 +1085,19 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F3">
         <v>40</v>
@@ -1105,19 +1111,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F4">
         <v>50</v>
@@ -1131,19 +1137,19 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F5">
         <v>60</v>
